--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135530557</v>
       </c>
       <c r="B2" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135530558</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135530559</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135530567</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135530570</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135530571</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135530572</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135530574</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135530576</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135530577</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135530579</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135530580</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135530582</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135530583</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>135530584</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135530585</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135530586</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135530587</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135530592</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135530594</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135530596</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>135530603</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135530604</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135530606</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>135530607</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135530611</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135530616</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>135530617</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>135530618</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>135530626</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135530578</v>
       </c>
       <c r="B32" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>135530560</v>
       </c>
       <c r="B33" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135530598</v>
       </c>
       <c r="B34" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135530608</v>
       </c>
       <c r="B35" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135530613</v>
       </c>
       <c r="B36" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135530599</v>
       </c>
       <c r="B37" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>135530600</v>
       </c>
       <c r="B38" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135530609</v>
       </c>
       <c r="B39" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135530562</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>135530563</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135530564</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>135530565</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135530566</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>135530573</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>135530588</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>135530590</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>135530605</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>135530610</v>
       </c>
       <c r="B49" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>135530612</v>
       </c>
       <c r="B50" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>135530614</v>
       </c>
       <c r="B51" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>135530615</v>
       </c>
       <c r="B52" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>135530619</v>
       </c>
       <c r="B53" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135530575</v>
       </c>
       <c r="B54" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>135530581</v>
       </c>
       <c r="B55" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>135530593</v>
       </c>
       <c r="B56" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>135530595</v>
       </c>
       <c r="B57" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>135530568</v>
       </c>
       <c r="B60" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135530557</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135530558</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135530559</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135530567</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135530570</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135530571</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135530572</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135530574</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135530576</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135530577</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135530579</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135530580</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135530582</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135530583</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>135530584</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135530585</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135530586</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135530587</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135530592</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135530594</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135530596</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>135530603</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135530604</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135530606</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>135530607</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135530611</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135530616</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>135530617</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>135530618</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>135530626</v>
       </c>
       <c r="B31" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135530578</v>
       </c>
       <c r="B32" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>135530560</v>
       </c>
       <c r="B33" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135530598</v>
       </c>
       <c r="B34" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135530608</v>
       </c>
       <c r="B35" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135530613</v>
       </c>
       <c r="B36" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135530599</v>
       </c>
       <c r="B37" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>135530600</v>
       </c>
       <c r="B38" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135530609</v>
       </c>
       <c r="B39" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>135530568</v>
       </c>
       <c r="B60" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135530557</v>
       </c>
       <c r="B2" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135530558</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135530559</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135530567</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135530570</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135530571</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135530572</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135530574</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135530576</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135530577</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135530579</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135530580</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135530582</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135530583</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>135530584</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135530585</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135530586</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135530587</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135530592</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135530594</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135530596</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>135530603</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135530604</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135530606</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>135530607</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135530611</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135530616</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>135530617</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>135530618</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>135530626</v>
       </c>
       <c r="B31" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135530578</v>
       </c>
       <c r="B32" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>135530560</v>
       </c>
       <c r="B33" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135530598</v>
       </c>
       <c r="B34" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135530608</v>
       </c>
       <c r="B35" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135530613</v>
       </c>
       <c r="B36" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135530599</v>
       </c>
       <c r="B37" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>135530600</v>
       </c>
       <c r="B38" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135530609</v>
       </c>
       <c r="B39" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135530562</v>
       </c>
       <c r="B40" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>135530563</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135530564</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>135530565</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135530566</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>135530573</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>135530588</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>135530590</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>135530605</v>
       </c>
       <c r="B48" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>135530610</v>
       </c>
       <c r="B49" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>135530612</v>
       </c>
       <c r="B50" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>135530614</v>
       </c>
       <c r="B51" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>135530615</v>
       </c>
       <c r="B52" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>135530619</v>
       </c>
       <c r="B53" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135530575</v>
       </c>
       <c r="B54" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>135530581</v>
       </c>
       <c r="B55" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>135530593</v>
       </c>
       <c r="B56" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>135530595</v>
       </c>
       <c r="B57" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>135530568</v>
       </c>
       <c r="B60" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135530557</v>
       </c>
       <c r="B2" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135530558</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135530559</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135530567</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135530570</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135530571</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135530572</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135530574</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135530576</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135530577</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135530579</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135530580</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135530582</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135530583</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>135530584</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135530585</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135530586</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135530587</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135530592</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135530594</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135530596</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>135530603</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135530604</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135530606</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>135530607</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135530611</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135530616</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>135530617</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>135530618</v>
       </c>
       <c r="B30" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>135530626</v>
       </c>
       <c r="B31" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135530578</v>
       </c>
       <c r="B32" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>135530560</v>
       </c>
       <c r="B33" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135530598</v>
       </c>
       <c r="B34" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135530608</v>
       </c>
       <c r="B35" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135530613</v>
       </c>
       <c r="B36" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135530599</v>
       </c>
       <c r="B37" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>135530600</v>
       </c>
       <c r="B38" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135530609</v>
       </c>
       <c r="B39" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135530562</v>
       </c>
       <c r="B40" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>135530563</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135530564</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>135530565</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135530566</v>
       </c>
       <c r="B44" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>135530573</v>
       </c>
       <c r="B45" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>135530588</v>
       </c>
       <c r="B46" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>135530590</v>
       </c>
       <c r="B47" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>135530605</v>
       </c>
       <c r="B48" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>135530610</v>
       </c>
       <c r="B49" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>135530612</v>
       </c>
       <c r="B50" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>135530614</v>
       </c>
       <c r="B51" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>135530615</v>
       </c>
       <c r="B52" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>135530619</v>
       </c>
       <c r="B53" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135530575</v>
       </c>
       <c r="B54" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>135530581</v>
       </c>
       <c r="B55" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>135530593</v>
       </c>
       <c r="B56" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>135530595</v>
       </c>
       <c r="B57" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>135530568</v>
       </c>
       <c r="B60" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135530557</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135530558</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135530559</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135530567</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135530570</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135530571</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135530572</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135530574</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135530576</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135530577</v>
       </c>
       <c r="B11" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135530579</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135530580</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135530582</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135530583</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>135530584</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135530585</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135530586</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135530587</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135530592</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135530594</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135530596</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>135530603</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135530604</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135530606</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>135530607</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135530611</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135530616</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>135530617</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>135530618</v>
       </c>
       <c r="B30" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>135530626</v>
       </c>
       <c r="B31" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135530578</v>
       </c>
       <c r="B32" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>135530560</v>
       </c>
       <c r="B33" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135530598</v>
       </c>
       <c r="B34" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135530608</v>
       </c>
       <c r="B35" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135530613</v>
       </c>
       <c r="B36" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135530599</v>
       </c>
       <c r="B37" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>135530600</v>
       </c>
       <c r="B38" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135530609</v>
       </c>
       <c r="B39" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135530562</v>
       </c>
       <c r="B40" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>135530563</v>
       </c>
       <c r="B41" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135530564</v>
       </c>
       <c r="B42" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>135530565</v>
       </c>
       <c r="B43" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135530566</v>
       </c>
       <c r="B44" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>135530573</v>
       </c>
       <c r="B45" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>135530588</v>
       </c>
       <c r="B46" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>135530590</v>
       </c>
       <c r="B47" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>135530605</v>
       </c>
       <c r="B48" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>135530610</v>
       </c>
       <c r="B49" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>135530612</v>
       </c>
       <c r="B50" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>135530614</v>
       </c>
       <c r="B51" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>135530615</v>
       </c>
       <c r="B52" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>135530619</v>
       </c>
       <c r="B53" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135530575</v>
       </c>
       <c r="B54" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>135530581</v>
       </c>
       <c r="B55" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>135530593</v>
       </c>
       <c r="B56" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>135530595</v>
       </c>
       <c r="B57" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>135530568</v>
       </c>
       <c r="B60" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135530557</v>
       </c>
       <c r="B2" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135530558</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135530559</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135530567</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135530570</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135530571</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135530572</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135530574</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135530576</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135530577</v>
       </c>
       <c r="B11" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135530579</v>
       </c>
       <c r="B12" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135530580</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135530582</v>
       </c>
       <c r="B14" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135530583</v>
       </c>
       <c r="B15" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>135530584</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135530585</v>
       </c>
       <c r="B17" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135530586</v>
       </c>
       <c r="B18" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135530587</v>
       </c>
       <c r="B19" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135530592</v>
       </c>
       <c r="B20" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135530594</v>
       </c>
       <c r="B21" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135530596</v>
       </c>
       <c r="B22" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>135530603</v>
       </c>
       <c r="B23" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135530604</v>
       </c>
       <c r="B24" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135530606</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>135530607</v>
       </c>
       <c r="B26" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135530611</v>
       </c>
       <c r="B27" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135530616</v>
       </c>
       <c r="B28" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>135530617</v>
       </c>
       <c r="B29" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>135530618</v>
       </c>
       <c r="B30" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>135530626</v>
       </c>
       <c r="B31" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135530578</v>
       </c>
       <c r="B32" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>135530560</v>
       </c>
       <c r="B33" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135530598</v>
       </c>
       <c r="B34" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135530608</v>
       </c>
       <c r="B35" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135530613</v>
       </c>
       <c r="B36" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135530599</v>
       </c>
       <c r="B37" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>135530600</v>
       </c>
       <c r="B38" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135530609</v>
       </c>
       <c r="B39" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>135530568</v>
       </c>
       <c r="B60" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135530557</v>
       </c>
       <c r="B2" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135530558</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135530559</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135530567</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135530570</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135530571</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135530572</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135530574</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135530576</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135530577</v>
       </c>
       <c r="B11" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135530579</v>
       </c>
       <c r="B12" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135530580</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135530582</v>
       </c>
       <c r="B14" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135530583</v>
       </c>
       <c r="B15" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>135530584</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135530585</v>
       </c>
       <c r="B17" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135530586</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135530587</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135530592</v>
       </c>
       <c r="B20" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135530594</v>
       </c>
       <c r="B21" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135530596</v>
       </c>
       <c r="B22" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>135530603</v>
       </c>
       <c r="B23" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>135530604</v>
       </c>
       <c r="B24" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135530606</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>135530607</v>
       </c>
       <c r="B26" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135530611</v>
       </c>
       <c r="B27" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135530616</v>
       </c>
       <c r="B28" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>135530617</v>
       </c>
       <c r="B29" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>135530618</v>
       </c>
       <c r="B30" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>135530626</v>
       </c>
       <c r="B31" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>135530578</v>
       </c>
       <c r="B32" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>135530560</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135530598</v>
       </c>
       <c r="B34" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135530608</v>
       </c>
       <c r="B35" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135530613</v>
       </c>
       <c r="B36" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135530599</v>
       </c>
       <c r="B37" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>135530600</v>
       </c>
       <c r="B38" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135530609</v>
       </c>
       <c r="B39" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135530562</v>
       </c>
       <c r="B40" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>135530563</v>
       </c>
       <c r="B41" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135530564</v>
       </c>
       <c r="B42" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>135530565</v>
       </c>
       <c r="B43" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135530566</v>
       </c>
       <c r="B44" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>135530573</v>
       </c>
       <c r="B45" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>135530588</v>
       </c>
       <c r="B46" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>135530590</v>
       </c>
       <c r="B47" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>135530605</v>
       </c>
       <c r="B48" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>135530610</v>
       </c>
       <c r="B49" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>135530612</v>
       </c>
       <c r="B50" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>135530614</v>
       </c>
       <c r="B51" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>135530615</v>
       </c>
       <c r="B52" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>135530619</v>
       </c>
       <c r="B53" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135530575</v>
       </c>
       <c r="B54" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>135530581</v>
       </c>
       <c r="B55" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>135530593</v>
       </c>
       <c r="B56" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>135530595</v>
       </c>
       <c r="B57" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>135530568</v>
       </c>
       <c r="B60" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -7402,7 +7402,7 @@
         <v>135530624</v>
       </c>
       <c r="B58" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135530625</v>
       </c>
       <c r="B59" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
